--- a/Outputs_primates/AllGenes_>49variants_Katie copy.xlsx
+++ b/Outputs_primates/AllGenes_>49variants_Katie copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Documents/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B565AAD-78F2-A840-A218-F53E4D8341E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C03D738-EA32-E647-A167-4E4589088CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15520" yWindow="7060" windowWidth="15340" windowHeight="17440" xr2:uid="{F0389E05-49D8-4340-AB03-1574F122DBB0}"/>
   </bookViews>
